--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484794_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484794_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6544</v>
+        <v>2.5257</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6358</v>
+        <v>3.1633</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9815</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>2.8393</v>
@@ -610,13 +610,13 @@
         <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7136</v>
+        <v>-0.8423</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0923</v>
+        <v>-0.5648</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6213</v>
+        <v>-0.2774</v>
       </c>
       <c r="V2" t="n">
         <v>-1.547</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2852</v>
+        <v>0.9543</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1451</v>
+        <v>1.8142</v>
       </c>
       <c r="F3" t="n">
         <v>-0.8599</v>
@@ -688,10 +688,10 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2257</v>
+        <v>-0.1052</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1328</v>
+        <v>-0.1981</v>
       </c>
       <c r="U3" t="n">
         <v>0.0929</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5246</v>
+        <v>0.7337</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4918</v>
+        <v>1.648</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9143</v>
       </c>
       <c r="G5" t="n">
         <v>2.1662</v>
@@ -844,13 +844,13 @@
         <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.472</v>
+        <v>-0.2629</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1764</v>
+        <v>-0.0201</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2957</v>
+        <v>-0.2428</v>
       </c>
       <c r="V5" t="n">
         <v>-1.547</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1503</v>
+        <v>-0.2974</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1411</v>
+        <v>-1.2184</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2913</v>
+        <v>0.921</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4903</v>
@@ -922,13 +922,13 @@
         <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4709</v>
+        <v>0.0232</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0029</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.468</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-0.019</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.9379</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5473</v>
+        <v>-1.7808</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7635</v>
+        <v>0.8429</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5574</v>
@@ -1000,13 +1000,13 @@
         <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0188</v>
+        <v>-0.1354</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2968</v>
+        <v>0.0633</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.278</v>
+        <v>-0.1987</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>J. CONNELLY IV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7462</v>
+        <v>-2.2668</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1854</v>
+        <v>-2.1243</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4391</v>
+        <v>-0.1425</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.264</v>
+        <v>-4.9989</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2897</v>
+        <v>-2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0257</v>
+        <v>-2.6589</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1186</v>
+        <v>-1.5858</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2317</v>
+        <v>-0.4852</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3502</v>
+        <v>-1.1005</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3826</v>
+        <v>-3.4131</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.058</v>
+        <v>-1.8547</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3245</v>
+        <v>-1.5584</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.7175</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0192</v>
+        <v>3.3966</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8576</v>
+        <v>-0.0227</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4325</v>
+        <v>-0.1985</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4251</v>
+        <v>0.1758</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.019</v>
+        <v>1.547</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CONNELLY IV</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1613</v>
+        <v>-2.5429</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8336</v>
+        <v>-3.691</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3277</v>
+        <v>1.1481</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9989</v>
+        <v>-0.264</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.34</v>
+        <v>-1.2897</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6589</v>
+        <v>1.0257</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5858</v>
+        <v>1.1186</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4852</v>
+        <v>-0.2317</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1005</v>
+        <v>1.3502</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4131</v>
+        <v>-1.3826</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8547</v>
+        <v>-1.058</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5584</v>
+        <v>-0.3245</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5096</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3966</v>
+        <v>3.0192</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0828</v>
+        <v>0.061</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0922</v>
+        <v>-0.0731</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0094</v>
+        <v>0.1341</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2452</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.547</v>
+        <v>-0.019</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5669</v>
+        <v>-2.9601</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5824</v>
+        <v>-2.0549</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9845</v>
+        <v>-0.9051</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5561</v>
@@ -1234,13 +1234,13 @@
         <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0299</v>
+        <v>-0.4231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.2927</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2098</v>
+        <v>-0.1305</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2452</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.253</v>
+        <v>-3.521</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5579</v>
+        <v>-0.6407</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6951</v>
+        <v>-2.8803</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2344</v>
@@ -1312,13 +1312,13 @@
         <v>2.4531</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.736</v>
+        <v>-0.004</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3274</v>
+        <v>-0.4103</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5914</v>
+        <v>0.4063</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7922</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. FERRIZ SELLES</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8924</v>
+        <v>-4.45</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0249</v>
+        <v>-3.9414</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8674</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4384</v>
+        <v>-3.8382</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0981</v>
+        <v>0.1996</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3403</v>
+        <v>-4.0378</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4029</v>
+        <v>-1.9802</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2357</v>
+        <v>1.062</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1672</v>
+        <v>-3.0422</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0354</v>
+        <v>-1.858</v>
       </c>
       <c r="N12" t="n">
         <v>-0.8624000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.173</v>
+        <v>-0.9956</v>
       </c>
       <c r="P12" t="n">
         <v>1.1322</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1322</v>
+        <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7184</v>
+        <v>-0.178</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.622</v>
+        <v>-0.3761</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0964</v>
+        <v>0.1981</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8678</v>
+        <v>-1.566</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8678</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>A. FERRIZ SELLES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2496</v>
+        <v>-4.5127</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.741</v>
+        <v>-2.7511</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-1.7616</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8382</v>
+        <v>-3.4384</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1996</v>
+        <v>-2.0981</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.0378</v>
+        <v>-1.3403</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9802</v>
+        <v>-2.4029</v>
       </c>
       <c r="K13" t="n">
-        <v>1.062</v>
+        <v>-1.2357</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0422</v>
+        <v>-1.1672</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.858</v>
+        <v>-1.0354</v>
       </c>
       <c r="N13" t="n">
         <v>-0.8624000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9956</v>
+        <v>-0.173</v>
       </c>
       <c r="P13" t="n">
         <v>1.1322</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9776</v>
+        <v>-0.3388</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1758</v>
+        <v>-0.3482</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1981</v>
+        <v>0.0094</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.566</v>
+        <v>-1.8678</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9244</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.1048</v>
+        <v>-16.3412</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.407</v>
+        <v>-10.6432</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.698000000000001</v>
+        <v>-5.697900000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-13.5676</v>
@@ -1516,7 +1516,7 @@
         <v>-4.147599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.4201</v>
+        <v>-9.420099999999998</v>
       </c>
       <c r="J14" t="n">
         <v>0.1152999999999995</v>
@@ -1546,13 +1546,13 @@
         <v>19.8135</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.9917</v>
+        <v>-2.2282</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.256799999999999</v>
+        <v>-2.493</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2648999999999999</v>
+        <v>0.2648</v>
       </c>
       <c r="V14" t="n">
         <v>-10.924</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.996</v>
+        <v>5.5715</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6602</v>
+        <v>5.4362</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3358</v>
+        <v>0.1353</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4393</v>
+        <v>4.7646</v>
       </c>
       <c r="H15" t="n">
-        <v>3.164</v>
+        <v>2.9113</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7248</v>
+        <v>1.8534</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3897</v>
+        <v>4.8142</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4832</v>
+        <v>2.8314</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.0935</v>
+        <v>1.9828</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0496</v>
+        <v>-0.0495</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.0798</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3687</v>
+        <v>-0.1294</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5661</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7454</v>
+        <v>0.1277</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0312</v>
+        <v>-0.2832</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2452</v>
+        <v>2.7922</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8342</v>
+        <v>5.3389</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1439</v>
+        <v>1.9525</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3097</v>
+        <v>3.3864</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7646</v>
+        <v>2.4393</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9113</v>
+        <v>3.164</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8534</v>
+        <v>-0.7248</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8142</v>
+        <v>1.3897</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8314</v>
+        <v>2.4832</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9828</v>
+        <v>-1.0935</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0495</v>
+        <v>1.0496</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0798</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1294</v>
+        <v>0.3687</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5661</v>
+        <v>0.5661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6096</v>
+        <v>1.0883</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5755</v>
+        <v>0.2611</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.034</v>
+        <v>0.8272</v>
       </c>
       <c r="V16" t="n">
         <v>1.2452</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7922</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>J. IBANEZ TEJERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3396</v>
+        <v>2.319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6765</v>
+        <v>1.4797</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6631</v>
+        <v>0.8394</v>
       </c>
       <c r="G17" t="n">
-        <v>0.543</v>
+        <v>1.8942</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5275</v>
+        <v>2.1365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0156</v>
+        <v>-0.2423</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4041</v>
+        <v>2.4634</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1221</v>
+        <v>2.4464</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5262</v>
+        <v>0.017</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9471000000000001</v>
+        <v>-0.5692</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4054</v>
+        <v>-0.3099</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5417</v>
+        <v>-0.2593</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3966</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.7175</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4766</v>
+        <v>0.3117</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0815</v>
+        <v>-0.342</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3951</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>3.7166</v>
+        <v>0.3018</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7166</v>
+        <v>0.3018</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. IBANEZ TEJERO</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6346</v>
+        <v>2.2228</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1874</v>
+        <v>-0.8824</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4473</v>
+        <v>3.1052</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8942</v>
+        <v>0.543</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1365</v>
+        <v>0.5275</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2423</v>
+        <v>0.0156</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4634</v>
+        <v>-0.4041</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4464</v>
+        <v>0.1221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.017</v>
+        <v>-0.5262</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5692</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3099</v>
+        <v>0.4054</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2593</v>
+        <v>0.5417</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1887</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-4.7175</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3727</v>
+        <v>1.3597</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6343</v>
+        <v>0.5225</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2616</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3018</v>
+        <v>3.7166</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>3.7166</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5098</v>
+        <v>1.6156</v>
       </c>
       <c r="E19" t="n">
         <v>1.2608</v>
       </c>
       <c r="F19" t="n">
-        <v>0.249</v>
+        <v>0.3548</v>
       </c>
       <c r="G19" t="n">
         <v>1.5569</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.047</v>
+        <v>0.0588</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1764</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8389</v>
+        <v>1.2008</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1429</v>
+        <v>-0.0455</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9818</v>
+        <v>1.2463</v>
       </c>
       <c r="G20" t="n">
         <v>0.8977000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2475</v>
+        <v>0.1145</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.164</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0835</v>
+        <v>0.1811</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7423</v>
+        <v>1.1849</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0917</v>
+        <v>0.2981</v>
       </c>
       <c r="F21" t="n">
-        <v>0.834</v>
+        <v>0.8869</v>
       </c>
       <c r="G21" t="n">
         <v>3.9475</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4503</v>
+        <v>-0.0076</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6343</v>
+        <v>-0.2446</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1841</v>
+        <v>0.237</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3018</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARREÑO</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.617</v>
+        <v>0.8544</v>
       </c>
       <c r="E22" t="n">
-        <v>0.617</v>
+        <v>-2.0073</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.8617</v>
       </c>
       <c r="G22" t="n">
-        <v>0.617</v>
+        <v>-1.2296</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.1824</v>
       </c>
       <c r="I22" t="n">
-        <v>0.617</v>
+        <v>-1.0473</v>
       </c>
       <c r="J22" t="n">
-        <v>0.617</v>
+        <v>-1.2184</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.0838</v>
       </c>
       <c r="L22" t="n">
-        <v>0.617</v>
+        <v>-1.1346</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-0.0113</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.0873</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.4425</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.1472</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.5897</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.2076</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="23">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VALDERRAMA CARREÑO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.57</v>
+        <v>0.617</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3324</v>
+        <v>0.617</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2376</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2586</v>
+        <v>0.617</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6724</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4138</v>
+        <v>0.617</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.11</v>
+        <v>0.617</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8914</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7815</v>
+        <v>0.617</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1487</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.781</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3676</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6025</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7824</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8201000000000001</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0545</v>
+        <v>0.0482</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4945</v>
+        <v>-0.0296</v>
       </c>
       <c r="F25" t="n">
-        <v>2.549</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.2296</v>
+        <v>-0.6817</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1824</v>
+        <v>-0.3983</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0473</v>
+        <v>-0.2834</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2184</v>
+        <v>0.1468</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0838</v>
+        <v>0.1057</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1346</v>
+        <v>0.0411</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0113</v>
+        <v>-0.8285</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.504</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0873</v>
+        <v>-0.3245</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3574</v>
+        <v>0.0318</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6343</v>
+        <v>-0.1764</v>
       </c>
       <c r="U25" t="n">
-        <v>0.277</v>
+        <v>0.2081</v>
       </c>
       <c r="V25" t="n">
-        <v>2.2076</v>
+        <v>0.3208</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.9624</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.214</v>
+        <v>-0.1492</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0296</v>
+        <v>-0.2522</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1844</v>
+        <v>0.1029</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6817</v>
+        <v>-1.2586</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3983</v>
+        <v>-1.6724</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2834</v>
+        <v>0.4138</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1468</v>
+        <v>-0.11</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1057</v>
+        <v>-0.8914</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0411</v>
+        <v>0.7815</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8285</v>
+        <v>-1.1487</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.504</v>
+        <v>-0.781</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3245</v>
+        <v>-0.3676</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3774</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2304</v>
+        <v>0.8833</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1764</v>
+        <v>0.1978</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0541</v>
+        <v>0.6855</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3208</v>
+        <v>1.547</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9775</v>
+        <v>-1.004</v>
       </c>
       <c r="E27" t="n">
         <v>-2.2027</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2252</v>
+        <v>1.1988</v>
       </c>
       <c r="G27" t="n">
         <v>-0.1849</v>
@@ -2560,13 +2560,13 @@
         <v>0.5661</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="T27" t="n">
         <v>0.074</v>
       </c>
       <c r="U27" t="n">
-        <v>0.756</v>
+        <v>0.7296</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3018</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.4574</v>
+        <v>-1.0328</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8358</v>
+        <v>-0.5435</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6216</v>
+        <v>-0.4893</v>
       </c>
       <c r="G28" t="n">
         <v>-0.3545</v>
@@ -2638,13 +2638,13 @@
         <v>0.1887</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.348</v>
+        <v>0.0766</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.2352</v>
+        <v>0.0572</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1129</v>
+        <v>0.0194</v>
       </c>
       <c r="V28" t="n">
         <v>0.9434</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>18.105</v>
+        <v>19.4041</v>
       </c>
       <c r="E29" t="n">
-        <v>5.698</v>
+        <v>5.698099999999998</v>
       </c>
       <c r="F29" t="n">
-        <v>12.4071</v>
+        <v>13.7062</v>
       </c>
       <c r="G29" t="n">
         <v>13.5679</v>
@@ -2692,13 +2692,13 @@
         <v>13.6831</v>
       </c>
       <c r="K29" t="n">
-        <v>5.7833</v>
+        <v>5.783300000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>7.8999</v>
+        <v>7.899900000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1155000000000002</v>
+        <v>-0.1155000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>-1.6356</v>
@@ -2713,16 +2713,16 @@
         <v>-19.8135</v>
       </c>
       <c r="R29" t="n">
-        <v>9.435</v>
+        <v>9.435000000000002</v>
       </c>
       <c r="S29" t="n">
-        <v>3.991700000000001</v>
+        <v>5.2909</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.2648999999999999</v>
+        <v>-0.2650000000000001</v>
       </c>
       <c r="U29" t="n">
-        <v>4.256600000000001</v>
+        <v>5.5559</v>
       </c>
       <c r="V29" t="n">
         <v>10.924</v>
